--- a/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/formato_global.xlsx
+++ b/POC_THINKING_SCOTIA/ejercicios_sesion_3/datos_salida/formato_global.xlsx
@@ -461,17 +461,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,20 +492,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Inversiones</t>
+          <t>Tarjetas</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Tarjetas</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -528,15 +522,12 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>31955094.22</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>31955094.22</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>125100882.37</v>
       </c>
     </row>
@@ -559,69 +550,60 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>44741539.5</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44741539.5</v>
-      </c>
-      <c r="H3" s="3" t="n">
         <v>116934113.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Comisiones por manejo</t>
+          <t>Intereses cobrados</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28803533.4</v>
+        <v>42160916.47</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>48120921.76</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>24550420.87</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>44155382.39</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>97509336.66</v>
+        <v>90281838.22999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Intereses cobrados</t>
+          <t>Comisiones por manejo</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>42160916.47</v>
+        <v>28803533.4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>48120921.76</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>44155382.39</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>90281838.22999999</v>
+        <v>72958915.78999999</v>
       </c>
     </row>
     <row r="6">
@@ -643,14 +625,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>49173228.32</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>49173228.32</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>49173228.32</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -674,9 +653,6 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
         <v>48277223.01</v>
       </c>
     </row>
@@ -696,22 +672,19 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>38239346.7</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>38239346.7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n">
         <v>38239346.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Rendimiento de inversiones</t>
+          <t>Ingreso por anualidad</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -724,29 +697,26 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>38106584.01</v>
+        <v>35924701.34</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>38106584.01</v>
+        <v>35924701.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Ingreso por anualidad</t>
+          <t>Ingreso por asesoría</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>35127631.16</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -755,387 +725,328 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>35924701.34</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>35924701.34</v>
+        <v>35127631.16</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Ingreso por asesoría</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>35127631.16</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>35127631.16</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>179085200.66</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>140466164.03</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>48277223.01</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>150274524.65</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>93914767.81999999</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>612017880.17</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>179085200.66</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>140466164.03</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>48277223.01</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>62657004.88</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>150274524.65</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>93914767.81999999</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>674674885.05</v>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Gastos de personal</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>55179793.87</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>56276308.16</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>43292523.59</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>53082083.82</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>43737304.96</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>251568014.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Gastos de personal</t>
+          <t>Servicios profesionales</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>73443041.31999999</v>
+        <v>46741450.73</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>69981908.48</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>43292523.59</v>
+        <v>41150474.37</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>57630057.38</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58033498.15</v>
+        <v>29147562.48</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>58124432.05</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>360505460.97</v>
+        <v>117039487.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Servicios profesionales</t>
+          <t>Gastos de publicidad</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>49180190.48999999</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>7117477.93</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>41150474.37</v>
+        <v>20854110.61</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>57511633.78</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8788881.91</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>39072870.45</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>145309895.15</v>
+        <v>78365744.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Licencias de software</t>
+          <t>Nómina y prestaciones</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2640985.62</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>17509700.79</v>
+        <v>50862171.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>11193820.37</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>51823761.52</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9833931.58</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6772963.49</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>99775163.37</v>
+        <v>50862171.1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Gastos de publicidad</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>20854110.61</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>57511633.78</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>78365744.39</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL GASTOS</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>101921244.6</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>107138479.26</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>105297108.57</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>110593717.6</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>72884867.44</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>497835417.47</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Nómina y prestaciones</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>50862171.1</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>50862171.1</v>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Multas regulatorias</t>
+          <t>Pérdida esperada</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8335850.789999999</v>
+        <v>78802530.18000001</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>5329020.64</v>
+        <v>25058724.37</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>66040151.96</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>18079294.35</v>
+        <v>0</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9794065.52</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>41538231.3</v>
+        <v>169901406.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Servicios de seguridad</t>
+          <t>Reserva crediticia</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>10802365.67</v>
+        <v>32820734.72</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3231347.82</v>
+        <v>29672361.75</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8993950.629999999</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>9019904.83</v>
+        <v>14053422.67</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7837788.37</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>39885357.31999999</v>
+        <v>76546519.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Servicios de TI externos</t>
+          <t>Reserva técnica seguros</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>3720758.73</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>796851.4</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>12449075.42</v>
+        <v>53843330.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>6889713.61</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3016790.71</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6905367.060000001</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>33778556.93</v>
+        <v>53843330.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Mantenimiento y limpieza</t>
+          <t>Provisión regulatoria</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3721838.6</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4782705.88</v>
+        <v>34531099.79</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>11131348.49</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6929311.67</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>26565204.64</v>
+        <v>34531099.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Renta de inmuebles</t>
+          <t>Ajuste de valuación</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4893298.24</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3816271.36</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6091170.46</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6560145.41</v>
+        <v>34084023.82</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1553245.58</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>22914131.05</v>
+        <v>34084023.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>TOTAL GASTOS</t>
+          <t>TOTAL PROVISIONES</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>153016490.86</v>
+        <v>111623264.9</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>162366588.12</v>
+        <v>54731086.12</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>148807831.33</v>
+        <v>88374430.69</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>136494785.83</v>
+        <v>80093574.63</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>169661964.26</v>
+        <v>34084023.82</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>129152255.82</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>899499916.2199999</v>
+        <v>368906380.16</v>
       </c>
     </row>
     <row r="25">
@@ -1146,212 +1057,30 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Pérdida esperada</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>98236437.92</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>55538723.95</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>10809975.44</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>72682449</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>237267586.31</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Ajuste de valuación</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>2304934.45</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>9965065.48</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>10818560.49</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>48340993.16</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>21314724.71</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>34084023.82</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>126828302.11</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Provisión regulatoria</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>10827016.22</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>17295188.32</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>42472228.72</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>4661444.92</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>7704086.33</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>19755216.03</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>102715180.54</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Reserva crediticia</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>36354435.09</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>35483721.16</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>10523720.55</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>17954846.87</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>100316723.67</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Reserva técnica seguros</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>53843330.9</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>53843330.9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL PROVISIONES</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>147722823.68</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>118282698.91</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>107134120.11</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>74336134.06999999</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>119656106.91</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>53839239.85</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>620971123.5299999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>RESULTADO NETO</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
-        <v>-121654113.88</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>-140183123</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>-207664728.43</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>-148173915.02</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>-139043546.52</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>-89076727.84999999</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>-845796154.6999998</v>
+      <c r="B26" s="7" t="n">
+        <v>-34459308.84</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>-21403401.35000001</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-145394316.25</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>-40412767.57999998</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>-13054123.44000001</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>-254723917.4600001</v>
       </c>
     </row>
   </sheetData>
